--- a/data/inventory.xlsx
+++ b/data/inventory.xlsx
@@ -453,7 +453,7 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>200</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>

--- a/data/inventory.xlsx
+++ b/data/inventory.xlsx
@@ -453,7 +453,7 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>42</v>
+        <v>1507</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>

--- a/data/inventory.xlsx
+++ b/data/inventory.xlsx
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
